--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851F2735-0EFF-48BE-8326-0ECD7233E03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6B46A8-16E8-4633-A828-FD495C5486CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="165">
   <si>
     <t>Категорија</t>
   </si>
@@ -589,6 +589,12 @@
   </si>
   <si>
     <t>https://ik-cod.github.io/Matematika/data/7</t>
+  </si>
+  <si>
+    <t>Релација за еквивалентвост и подредување</t>
+  </si>
+  <si>
+    <t>https://ik-cod.github.io/Matematika/data/gemini-code-1789115761271</t>
   </si>
 </sst>
 </file>
@@ -803,7 +809,6 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="7"/>
         <filter val="8"/>
       </filters>
     </filterColumn>
@@ -1116,7 +1121,7 @@
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1735,7 +1740,7 @@
       </c>
       <c r="E41" s="11"/>
     </row>
-    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>5</v>
       </c>
@@ -1752,7 +1757,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
@@ -1767,7 +1772,7 @@
       </c>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
@@ -1782,7 +1787,7 @@
       </c>
       <c r="E44" s="11"/>
     </row>
-    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>5</v>
       </c>
@@ -1797,7 +1802,7 @@
       </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1810,7 +1815,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1823,7 +1828,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1836,7 +1841,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -1849,7 +1854,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -1862,7 +1867,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -1875,7 +1880,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -1888,7 +1893,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -1901,7 +1906,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -1914,7 +1919,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="11"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -1927,7 +1932,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="11"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -1940,7 +1945,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -1953,7 +1958,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -1966,7 +1971,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -1979,7 +1984,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -1992,7 +1997,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -2005,7 +2010,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -2018,7 +2023,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -2031,7 +2036,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -2044,7 +2049,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -2057,7 +2062,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -2070,7 +2075,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -2083,7 +2088,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -2096,7 +2101,7 @@
       <c r="D68" s="5"/>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -2109,7 +2114,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2122,7 +2127,7 @@
       <c r="D70" s="5"/>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2135,7 +2140,7 @@
       <c r="D71" s="5"/>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2148,7 +2153,7 @@
       <c r="D72" s="5"/>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2161,7 +2166,7 @@
       <c r="D73" s="5"/>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2174,7 +2179,7 @@
       <c r="D74" s="5"/>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2187,7 +2192,7 @@
       <c r="D75" s="5"/>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2200,7 +2205,7 @@
       <c r="D76" s="5"/>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2213,7 +2218,7 @@
       <c r="D77" s="5"/>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2226,7 +2231,7 @@
       <c r="D78" s="5"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2239,7 +2244,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2252,7 +2257,7 @@
       <c r="D80" s="5"/>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2318,8 +2323,12 @@
       <c r="C85" s="4">
         <v>4</v>
       </c>
-      <c r="D85" s="5"/>
-      <c r="E85" s="11"/>
+      <c r="D85" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E85" s="11" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6B46A8-16E8-4633-A828-FD495C5486CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2BC9B5-893F-4448-8DF8-0FC59D949630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="167">
   <si>
     <t>Категорија</t>
   </si>
@@ -595,6 +595,12 @@
   </si>
   <si>
     <t>https://ik-cod.github.io/Matematika/data/gemini-code-1789115761271</t>
+  </si>
+  <si>
+    <t>Вежби за релации</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbwdZK8UDUHE_5Ky4z5genO0NyB9Qn4znFhUhSgvCJf5BCFms8R6Vw4-S0GQalpnRHEN/exec</t>
   </si>
 </sst>
 </file>
@@ -2340,8 +2346,12 @@
       <c r="C86" s="4">
         <v>5</v>
       </c>
-      <c r="D86" s="5"/>
-      <c r="E86" s="11"/>
+      <c r="D86" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2BC9B5-893F-4448-8DF8-0FC59D949630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971AE155-D015-474A-BC5C-22739282E483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -600,7 +600,7 @@
     <t>Вежби за релации</t>
   </si>
   <si>
-    <t>https://script.google.com/macros/s/AKfycbwdZK8UDUHE_5Ky4z5genO0NyB9Qn4znFhUhSgvCJf5BCFms8R6Vw4-S0GQalpnRHEN/exec</t>
+    <t>https://script.google.com/macros/s/AKfycbwivlQjcWhi72WQSK4uJKeXKFSecygPNRxguTqSO2WCt4s1ssSVmGlY9afFDSt9TJGk/exec</t>
   </si>
 </sst>
 </file>
@@ -2349,7 +2349,7 @@
       <c r="D86" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E86" s="11" t="s">
+      <c r="E86" s="13" t="s">
         <v>166</v>
       </c>
     </row>
@@ -10997,11 +10997,12 @@
   <hyperlinks>
     <hyperlink ref="E603" r:id="rId1" xr:uid="{C4BB2320-73F4-4247-B6EF-4A48501D6F90}"/>
     <hyperlink ref="E82" r:id="rId2" xr:uid="{822F4467-6A29-45B0-81B1-6A7C3274ED07}"/>
+    <hyperlink ref="E86" r:id="rId3" xr:uid="{128E47EA-44B5-445E-9813-7B5B6E392FE6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971AE155-D015-474A-BC5C-22739282E483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2472E7-88CD-422F-9D3B-E9C482A93CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -100,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="175">
   <si>
     <t>Категорија</t>
   </si>
@@ -601,6 +602,30 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbwivlQjcWhi72WQSK4uJKeXKFSecygPNRxguTqSO2WCt4s1ssSVmGlY9afFDSt9TJGk/exec</t>
+  </si>
+  <si>
+    <t>Рационални броеви</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbzwaOeDsvA9sh7Wf2iKq8qOjzdw4jvZ3EMXZfRXmOOfJ23A4v0-Xm7UvTSzG2OVxwVJ/exec</t>
+  </si>
+  <si>
+    <t>Претставување релации</t>
+  </si>
+  <si>
+    <t>Својства на релации</t>
+  </si>
+  <si>
+    <t>Релации во секојдневниот живот</t>
+  </si>
+  <si>
+    <t>Вежби за рационални броеви</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbxxgAjN9FZASm3iss8U4FMIyBqhxQcaUMQVLIj7BLlYClBxWdaCmwXqh92S5_Q0mm0E/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbzR7ncQWByyZtvu1pAZWKLrHgPWFhzN9sQsDfluBkaM7rRMWYWkz8r5gJgzmaxNzkNK/exec</t>
   </si>
 </sst>
 </file>
@@ -2303,7 +2328,9 @@
       <c r="C83" s="4">
         <v>2</v>
       </c>
-      <c r="D83" s="5"/>
+      <c r="D83" s="5" t="s">
+        <v>169</v>
+      </c>
       <c r="E83" s="11"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -2316,7 +2343,9 @@
       <c r="C84" s="4">
         <v>3</v>
       </c>
-      <c r="D84" s="5"/>
+      <c r="D84" s="5" t="s">
+        <v>170</v>
+      </c>
       <c r="E84" s="11"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -2330,11 +2359,9 @@
         <v>4</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E85" s="11" t="s">
-        <v>164</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="E85" s="11"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
@@ -2347,10 +2374,10 @@
         <v>5</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E86" s="13" t="s">
-        <v>166</v>
+        <v>163</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -2363,8 +2390,12 @@
       <c r="C87" s="4">
         <v>6</v>
       </c>
-      <c r="D87" s="5"/>
-      <c r="E87" s="11"/>
+      <c r="D87" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
@@ -2376,8 +2407,12 @@
       <c r="C88" s="4">
         <v>7</v>
       </c>
-      <c r="D88" s="5"/>
-      <c r="E88" s="11"/>
+      <c r="D88" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E88" s="11" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
@@ -2389,8 +2424,12 @@
       <c r="C89" s="4">
         <v>8</v>
       </c>
-      <c r="D89" s="5"/>
-      <c r="E89" s="11"/>
+      <c r="D89" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E89" s="11" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
@@ -2402,8 +2441,12 @@
       <c r="C90" s="4">
         <v>9</v>
       </c>
-      <c r="D90" s="5"/>
-      <c r="E90" s="11"/>
+      <c r="D90" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E90" s="11" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
@@ -10997,12 +11040,11 @@
   <hyperlinks>
     <hyperlink ref="E603" r:id="rId1" xr:uid="{C4BB2320-73F4-4247-B6EF-4A48501D6F90}"/>
     <hyperlink ref="E82" r:id="rId2" xr:uid="{822F4467-6A29-45B0-81B1-6A7C3274ED07}"/>
-    <hyperlink ref="E86" r:id="rId3" xr:uid="{128E47EA-44B5-445E-9813-7B5B6E392FE6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId4"/>
+  <legacyDrawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2472E7-88CD-422F-9D3B-E9C482A93CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BD333E-AD39-4B0C-A0E7-6D6E566F3D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -101,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="178">
   <si>
     <t>Категорија</t>
   </si>
@@ -626,13 +625,22 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbzR7ncQWByyZtvu1pAZWKLrHgPWFhzN9sQsDfluBkaM7rRMWYWkz8r5gJgzmaxNzkNK/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbwcgcWczhIB_FwMiUgY8LNbZG3r0xl59BUyvBAXC9oNEZLDGg9xi9KRnComUv-a123K/exec</t>
+  </si>
+  <si>
+    <t>Собирање на цели броеви со исти или различни знаци</t>
+  </si>
+  <si>
+    <t>Својства на операцијата собирање на цели броеви</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -685,6 +693,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -769,7 +784,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -808,6 +823,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -840,7 +856,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="8"/>
+        <filter val="7"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1152,7 +1168,7 @@
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1771,7 +1787,7 @@
       </c>
       <c r="E41" s="11"/>
     </row>
-    <row r="42" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>5</v>
       </c>
@@ -1788,7 +1804,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
@@ -1803,7 +1819,7 @@
       </c>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
@@ -1818,7 +1834,7 @@
       </c>
       <c r="E44" s="11"/>
     </row>
-    <row r="45" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>5</v>
       </c>
@@ -1833,7 +1849,7 @@
       </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1846,7 +1862,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1859,7 +1875,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1872,7 +1888,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -1885,7 +1901,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -1898,7 +1914,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -1911,7 +1927,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -1924,7 +1940,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -1937,7 +1953,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -1947,10 +1963,14 @@
       <c r="C54" s="4">
         <v>13</v>
       </c>
-      <c r="D54" s="5"/>
-      <c r="E54" s="11"/>
-    </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D54" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -1960,10 +1980,14 @@
       <c r="C55" s="4">
         <v>14</v>
       </c>
-      <c r="D55" s="5"/>
-      <c r="E55" s="11"/>
-    </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D55" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -1976,7 +2000,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -1989,7 +2013,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -2002,7 +2026,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -2015,7 +2039,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -2028,7 +2052,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -2041,7 +2065,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -2054,7 +2078,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -2067,7 +2091,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -2080,7 +2104,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -2093,7 +2117,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -2106,7 +2130,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -2119,7 +2143,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -2132,7 +2156,7 @@
       <c r="D68" s="5"/>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -2145,7 +2169,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2158,7 +2182,7 @@
       <c r="D70" s="5"/>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2171,7 +2195,7 @@
       <c r="D71" s="5"/>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2184,7 +2208,7 @@
       <c r="D72" s="5"/>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2197,7 +2221,7 @@
       <c r="D73" s="5"/>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2210,7 +2234,7 @@
       <c r="D74" s="5"/>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2223,7 +2247,7 @@
       <c r="D75" s="5"/>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2236,7 +2260,7 @@
       <c r="D76" s="5"/>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2249,7 +2273,7 @@
       <c r="D77" s="5"/>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2262,7 +2286,7 @@
       <c r="D78" s="5"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2275,7 +2299,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2288,7 +2312,7 @@
       <c r="D80" s="5"/>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2301,7 +2325,7 @@
       <c r="D81" s="5"/>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2318,7 +2342,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2333,7 +2357,7 @@
       </c>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2348,7 +2372,7 @@
       </c>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2363,7 +2387,7 @@
       </c>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2380,7 +2404,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -2397,7 +2421,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -2414,7 +2438,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2431,7 +2455,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2448,7 +2472,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2461,7 +2485,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2474,7 +2498,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2487,7 +2511,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2500,7 +2524,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2513,7 +2537,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2526,7 +2550,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2539,7 +2563,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2552,7 +2576,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2565,7 +2589,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2578,7 +2602,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2591,7 +2615,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2604,7 +2628,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2617,7 +2641,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2630,7 +2654,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2643,7 +2667,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2656,7 +2680,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2669,7 +2693,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2682,7 +2706,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2695,7 +2719,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2708,7 +2732,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2721,7 +2745,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2734,7 +2758,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2747,7 +2771,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2760,7 +2784,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2773,7 +2797,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2786,7 +2810,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2799,7 +2823,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -2812,7 +2836,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -2825,7 +2849,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -2838,7 +2862,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>
@@ -11042,9 +11066,10 @@
     <hyperlink ref="E82" r:id="rId2" xr:uid="{822F4467-6A29-45B0-81B1-6A7C3274ED07}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BD333E-AD39-4B0C-A0E7-6D6E566F3D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FA6B73-4C93-4E0C-A693-C71A88B02A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="179">
   <si>
     <t>Категорија</t>
   </si>
@@ -634,6 +634,9 @@
   </si>
   <si>
     <t>Својства на операцијата собирање на цели броеви</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbxo0z1pgZewBO0gRnvnxCXFdu23MTRHTvpyezJcPMZngBdpWONVuCPI_udCVz8O200Z/exec</t>
   </si>
 </sst>
 </file>
@@ -1984,7 +1987,7 @@
         <v>177</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FA6B73-4C93-4E0C-A693-C71A88B02A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA11600-F3D9-4DA0-9C84-F6F2791F8B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -621,9 +621,6 @@
     <t>Вежби за рационални броеви</t>
   </si>
   <si>
-    <t>https://script.google.com/macros/s/AKfycbxxgAjN9FZASm3iss8U4FMIyBqhxQcaUMQVLIj7BLlYClBxWdaCmwXqh92S5_Q0mm0E/exec</t>
-  </si>
-  <si>
     <t>https://script.google.com/macros/s/AKfycbzR7ncQWByyZtvu1pAZWKLrHgPWFhzN9sQsDfluBkaM7rRMWYWkz8r5gJgzmaxNzkNK/exec</t>
   </si>
   <si>
@@ -637,6 +634,9 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbxo0z1pgZewBO0gRnvnxCXFdu23MTRHTvpyezJcPMZngBdpWONVuCPI_udCVz8O200Z/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbwIIb_4kK9fzwI8dFex57oYIbnFKRHysaFytdOhtYISwGBLFZht0UFvOq1w8NY8RyzQ/exec</t>
   </si>
 </sst>
 </file>
@@ -859,7 +859,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="7"/>
+        <filter val="8"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1171,7 +1171,7 @@
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="E41" s="11"/>
     </row>
-    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>5</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E44" s="11"/>
     </row>
-    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>5</v>
       </c>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1865,7 +1865,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1878,7 +1878,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1891,7 +1891,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -1904,7 +1904,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -1917,7 +1917,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -1930,7 +1930,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -1943,7 +1943,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -1956,7 +1956,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -1967,13 +1967,13 @@
         <v>13</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -1984,13 +1984,13 @@
         <v>14</v>
       </c>
       <c r="D55" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="E55" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="E55" s="11" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -2003,7 +2003,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -2016,7 +2016,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -2029,7 +2029,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -2042,7 +2042,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -2055,7 +2055,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -2068,7 +2068,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -2081,7 +2081,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -2094,7 +2094,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -2107,7 +2107,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -2120,7 +2120,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -2133,7 +2133,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -2146,7 +2146,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -2159,7 +2159,7 @@
       <c r="D68" s="5"/>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -2172,7 +2172,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2185,7 +2185,7 @@
       <c r="D70" s="5"/>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2198,7 +2198,7 @@
       <c r="D71" s="5"/>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2211,7 +2211,7 @@
       <c r="D72" s="5"/>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2224,7 +2224,7 @@
       <c r="D73" s="5"/>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2237,7 +2237,7 @@
       <c r="D74" s="5"/>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2250,7 +2250,7 @@
       <c r="D75" s="5"/>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2263,7 +2263,7 @@
       <c r="D76" s="5"/>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2276,7 +2276,7 @@
       <c r="D77" s="5"/>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2289,7 +2289,7 @@
       <c r="D78" s="5"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2302,7 +2302,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2315,7 +2315,7 @@
       <c r="D80" s="5"/>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2328,7 +2328,7 @@
       <c r="D81" s="5"/>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -2438,10 +2438,10 @@
         <v>171</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2472,10 +2472,10 @@
         <v>172</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2488,7 +2488,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2501,7 +2501,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2514,7 +2514,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2527,7 +2527,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2540,7 +2540,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2553,7 +2553,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2566,7 +2566,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2579,7 +2579,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2592,7 +2592,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2605,7 +2605,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2618,7 +2618,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2631,7 +2631,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2644,7 +2644,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2657,7 +2657,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2670,7 +2670,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2683,7 +2683,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2696,7 +2696,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2709,7 +2709,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2722,7 +2722,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2735,7 +2735,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2748,7 +2748,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2761,7 +2761,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2774,7 +2774,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2787,7 +2787,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2800,7 +2800,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2813,7 +2813,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2826,7 +2826,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -2839,7 +2839,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -2852,7 +2852,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -2865,7 +2865,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA11600-F3D9-4DA0-9C84-F6F2791F8B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFBB0EC-D68E-4E3D-A9EB-453CC4A07111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -633,10 +633,10 @@
     <t>Својства на операцијата собирање на цели броеви</t>
   </si>
   <si>
-    <t>https://script.google.com/macros/s/AKfycbxo0z1pgZewBO0gRnvnxCXFdu23MTRHTvpyezJcPMZngBdpWONVuCPI_udCVz8O200Z/exec</t>
-  </si>
-  <si>
     <t>https://script.google.com/macros/s/AKfycbwIIb_4kK9fzwI8dFex57oYIbnFKRHysaFytdOhtYISwGBLFZht0UFvOq1w8NY8RyzQ/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbzIbgoF-gk5_XlLinTNGGwP91FUnXzntd-em8O4ytk3ClSAJTYMNvXb4bBwbYh5wZ-xXQ/exec</t>
   </si>
 </sst>
 </file>
@@ -859,7 +859,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="8"/>
+        <filter val="7"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1171,7 +1171,7 @@
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="E41" s="11"/>
     </row>
-    <row r="42" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>5</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E44" s="11"/>
     </row>
-    <row r="45" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>5</v>
       </c>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1865,7 +1865,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1878,7 +1878,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1891,7 +1891,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -1904,7 +1904,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -1917,7 +1917,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -1930,7 +1930,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -1943,7 +1943,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -1956,7 +1956,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -1987,10 +1987,10 @@
         <v>176</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -2003,7 +2003,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -2016,7 +2016,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -2029,7 +2029,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -2042,7 +2042,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -2055,7 +2055,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -2068,7 +2068,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -2081,7 +2081,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -2094,7 +2094,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -2107,7 +2107,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -2120,7 +2120,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -2133,7 +2133,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -2146,7 +2146,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -2159,7 +2159,7 @@
       <c r="D68" s="5"/>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -2172,7 +2172,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2185,7 +2185,7 @@
       <c r="D70" s="5"/>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2198,7 +2198,7 @@
       <c r="D71" s="5"/>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2211,7 +2211,7 @@
       <c r="D72" s="5"/>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2224,7 +2224,7 @@
       <c r="D73" s="5"/>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2237,7 +2237,7 @@
       <c r="D74" s="5"/>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2250,7 +2250,7 @@
       <c r="D75" s="5"/>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2263,7 +2263,7 @@
       <c r="D76" s="5"/>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2276,7 +2276,7 @@
       <c r="D77" s="5"/>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2289,7 +2289,7 @@
       <c r="D78" s="5"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2302,7 +2302,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2315,7 +2315,7 @@
       <c r="D80" s="5"/>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2328,7 +2328,7 @@
       <c r="D81" s="5"/>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2472,10 +2472,10 @@
         <v>172</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2488,7 +2488,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2501,7 +2501,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2514,7 +2514,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2527,7 +2527,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2540,7 +2540,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2553,7 +2553,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2566,7 +2566,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2579,7 +2579,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2592,7 +2592,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2605,7 +2605,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2618,7 +2618,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2631,7 +2631,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2644,7 +2644,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2657,7 +2657,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2670,7 +2670,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2683,7 +2683,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2696,7 +2696,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2709,7 +2709,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2722,7 +2722,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2735,7 +2735,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2748,7 +2748,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2761,7 +2761,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2774,7 +2774,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2787,7 +2787,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2800,7 +2800,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2813,7 +2813,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2826,7 +2826,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -2839,7 +2839,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -2852,7 +2852,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -2865,7 +2865,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFBB0EC-D68E-4E3D-A9EB-453CC4A07111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC60A75-4394-4F52-94F3-0AF1518ACF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -633,10 +633,10 @@
     <t>Својства на операцијата собирање на цели броеви</t>
   </si>
   <si>
-    <t>https://script.google.com/macros/s/AKfycbwIIb_4kK9fzwI8dFex57oYIbnFKRHysaFytdOhtYISwGBLFZht0UFvOq1w8NY8RyzQ/exec</t>
-  </si>
-  <si>
-    <t>https://script.google.com/macros/s/AKfycbzIbgoF-gk5_XlLinTNGGwP91FUnXzntd-em8O4ytk3ClSAJTYMNvXb4bBwbYh5wZ-xXQ/exec</t>
+    <t>https://script.google.com/macros/s/AKfycbzQOZEgdbgU9VgkulazGzh7s1u-kRCWnxBZFWZHyfYnr9H2GCRtzgnI23LMs0JOo1TIfA/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbwDAOOIooO8COqTJfrB9ThISFKHembNgicBuNZJ2OL_CtHGdh09SCUUuaDKjw6ZL5Z1/exec</t>
   </si>
 </sst>
 </file>
@@ -859,7 +859,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="7"/>
+        <filter val="8"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1171,7 +1171,7 @@
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="E41" s="11"/>
     </row>
-    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>5</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E44" s="11"/>
     </row>
-    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>5</v>
       </c>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1865,7 +1865,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1878,7 +1878,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1891,7 +1891,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -1904,7 +1904,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -1917,7 +1917,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -1930,7 +1930,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -1943,7 +1943,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -1956,7 +1956,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -1987,10 +1987,10 @@
         <v>176</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -2003,7 +2003,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -2016,7 +2016,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -2029,7 +2029,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -2042,7 +2042,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -2055,7 +2055,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -2068,7 +2068,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -2081,7 +2081,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -2094,7 +2094,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -2107,7 +2107,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -2120,7 +2120,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -2133,7 +2133,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -2146,7 +2146,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -2159,7 +2159,7 @@
       <c r="D68" s="5"/>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -2172,7 +2172,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2185,7 +2185,7 @@
       <c r="D70" s="5"/>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2198,7 +2198,7 @@
       <c r="D71" s="5"/>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2211,7 +2211,7 @@
       <c r="D72" s="5"/>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2224,7 +2224,7 @@
       <c r="D73" s="5"/>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2237,7 +2237,7 @@
       <c r="D74" s="5"/>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2250,7 +2250,7 @@
       <c r="D75" s="5"/>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2263,7 +2263,7 @@
       <c r="D76" s="5"/>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2276,7 +2276,7 @@
       <c r="D77" s="5"/>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2289,7 +2289,7 @@
       <c r="D78" s="5"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2302,7 +2302,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2315,7 +2315,7 @@
       <c r="D80" s="5"/>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2328,7 +2328,7 @@
       <c r="D81" s="5"/>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2472,10 +2472,10 @@
         <v>172</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2488,7 +2488,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2501,7 +2501,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2514,7 +2514,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2527,7 +2527,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2540,7 +2540,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2553,7 +2553,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2566,7 +2566,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2579,7 +2579,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2592,7 +2592,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2605,7 +2605,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2618,7 +2618,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2631,7 +2631,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2644,7 +2644,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2657,7 +2657,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2670,7 +2670,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2683,7 +2683,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2696,7 +2696,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2709,7 +2709,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2722,7 +2722,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2735,7 +2735,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2748,7 +2748,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2761,7 +2761,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2774,7 +2774,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2787,7 +2787,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2800,7 +2800,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2813,7 +2813,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2826,7 +2826,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -2839,7 +2839,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -2852,7 +2852,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -2865,7 +2865,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC60A75-4394-4F52-94F3-0AF1518ACF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE167E8-BCB1-4338-BCC4-CAEBEFA3C8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="199">
   <si>
     <t>Категорија</t>
   </si>
@@ -579,9 +579,6 @@
     <t>https://script.google.com/macros/s/AKfycbwm1HrLVb56EXheipy9go4kYrPgHu4cmqg1ocgHqKaM0OfZQfsXj-cWl6DOdDsGJvPEgw/exec</t>
   </si>
   <si>
-    <t>Поим за релација</t>
-  </si>
-  <si>
     <t>https://ik-cod.github.io/Matematika/data/8</t>
   </si>
   <si>
@@ -591,15 +588,9 @@
     <t>https://ik-cod.github.io/Matematika/data/7</t>
   </si>
   <si>
-    <t>Релација за еквивалентвост и подредување</t>
-  </si>
-  <si>
     <t>https://ik-cod.github.io/Matematika/data/gemini-code-1789115761271</t>
   </si>
   <si>
-    <t>Вежби за релации</t>
-  </si>
-  <si>
     <t>https://script.google.com/macros/s/AKfycbwivlQjcWhi72WQSK4uJKeXKFSecygPNRxguTqSO2WCt4s1ssSVmGlY9afFDSt9TJGk/exec</t>
   </si>
   <si>
@@ -609,15 +600,6 @@
     <t>https://script.google.com/macros/s/AKfycbzwaOeDsvA9sh7Wf2iKq8qOjzdw4jvZ3EMXZfRXmOOfJ23A4v0-Xm7UvTSzG2OVxwVJ/exec</t>
   </si>
   <si>
-    <t>Претставување релации</t>
-  </si>
-  <si>
-    <t>Својства на релации</t>
-  </si>
-  <si>
-    <t>Релации во секојдневниот живот</t>
-  </si>
-  <si>
     <t>Вежби за рационални броеви</t>
   </si>
   <si>
@@ -637,13 +619,91 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbwDAOOIooO8COqTJfrB9ThISFKHembNgicBuNZJ2OL_CtHGdh09SCUUuaDKjw6ZL5Z1/exec</t>
+  </si>
+  <si>
+    <t>Одземање на цели броеви</t>
+  </si>
+  <si>
+    <t>Множење на цели броеви</t>
+  </si>
+  <si>
+    <t>Својства на операцијата множење на цели броеви</t>
+  </si>
+  <si>
+    <t>Делење на цели броеви</t>
+  </si>
+  <si>
+    <t>Решавање равенки во Z</t>
+  </si>
+  <si>
+    <t>Степен со показател природен број</t>
+  </si>
+  <si>
+    <t>Квадрати и квадратни корени до 100</t>
+  </si>
+  <si>
+    <t>Споредување на дропки</t>
+  </si>
+  <si>
+    <t>Еднодневен излет</t>
+  </si>
+  <si>
+    <t>Претставување децимални броеви</t>
+  </si>
+  <si>
+    <t>Опишување, претставување и споредување делови од целината со дропки и проценти</t>
+  </si>
+  <si>
+    <t>Претставување дел од целина како дропка или процент</t>
+  </si>
+  <si>
+    <t>Процент</t>
+  </si>
+  <si>
+    <t>Собирање и одземање дропки</t>
+  </si>
+  <si>
+    <t>Множење и делење дропки со природен број. Реципрочна дропка.</t>
+  </si>
+  <si>
+    <t>Множење и делење дропки</t>
+  </si>
+  <si>
+    <t>Собирање и одземање на децимални броеви со различен број на децимали</t>
+  </si>
+  <si>
+    <t>Множење и делење на децимални броеви</t>
+  </si>
+  <si>
+    <t>Врска меѓу размер и дел од целина</t>
+  </si>
+  <si>
+    <t>Примена на право пропорционалност во реални ситуации</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbznanFehKu46uR9ojkTXUyOEzNR5dppsAFM5HLdc-7-g1ai9MoqDhJlW2xU4jbvzeLXNw/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbzWu-Uo2ZMqu-xFx7PO2bQ8uvY82UlH5CYZzZGiTUXblUgKQdSjCj5xaJ7Q2meywc0r/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbzy8gZFRDPz_2ab2j6LZWFwj6Jp1WbsUIg2HNe9UriZFeKohBPwVIcBUdXC4tzp0PVB/exec</t>
+  </si>
+  <si>
+    <t>Бесконечни периодични децимални броеви</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbxps3m-aLDJ60M-rwB1i2chsPVpltTpyxgpK7boq4rWBPCoIB6NddqZW8Iw2pA0C2NT/exec</t>
+  </si>
+  <si>
+    <t>Операции со дропки</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -707,6 +767,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -741,7 +808,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -782,12 +849,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -827,6 +922,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -850,8 +955,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LessonsTable" displayName="LessonsTable" ref="A1:E736">
-  <autoFilter ref="A1:E736" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LessonsTable" displayName="LessonsTable" ref="A1:E744">
+  <autoFilter ref="A1:E744" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
         <filter val="Броеви"/>
@@ -859,7 +964,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="8"/>
+        <filter val="9"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1162,7 +1267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E736"/>
+  <dimension ref="A1:E744"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1801,10 +1906,10 @@
         <v>1</v>
       </c>
       <c r="D42" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="E42" s="11" t="s">
         <v>161</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1967,10 +2072,10 @@
         <v>13</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
@@ -1984,13 +2089,13 @@
         <v>14</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -2000,10 +2105,14 @@
       <c r="C56" s="4">
         <v>15</v>
       </c>
-      <c r="D56" s="5"/>
-      <c r="E56" s="11"/>
-    </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D56" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -2013,10 +2122,14 @@
       <c r="C57" s="4">
         <v>16</v>
       </c>
-      <c r="D57" s="5"/>
-      <c r="E57" s="11"/>
-    </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D57" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -2026,10 +2139,12 @@
       <c r="C58" s="4">
         <v>17</v>
       </c>
-      <c r="D58" s="5"/>
+      <c r="D58" s="16" t="s">
+        <v>175</v>
+      </c>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -2039,10 +2154,12 @@
       <c r="C59" s="4">
         <v>18</v>
       </c>
-      <c r="D59" s="5"/>
+      <c r="D59" s="16" t="s">
+        <v>176</v>
+      </c>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -2052,10 +2169,12 @@
       <c r="C60" s="4">
         <v>19</v>
       </c>
-      <c r="D60" s="5"/>
+      <c r="D60" s="16" t="s">
+        <v>82</v>
+      </c>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -2065,10 +2184,12 @@
       <c r="C61" s="4">
         <v>20</v>
       </c>
-      <c r="D61" s="5"/>
+      <c r="D61" s="16" t="s">
+        <v>82</v>
+      </c>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -2078,10 +2199,12 @@
       <c r="C62" s="4">
         <v>21</v>
       </c>
-      <c r="D62" s="5"/>
+      <c r="D62" s="17" t="s">
+        <v>15</v>
+      </c>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -2091,10 +2214,12 @@
       <c r="C63" s="4">
         <v>22</v>
       </c>
-      <c r="D63" s="5"/>
+      <c r="D63" s="17" t="s">
+        <v>177</v>
+      </c>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -2104,10 +2229,12 @@
       <c r="C64" s="4">
         <v>23</v>
       </c>
-      <c r="D64" s="5"/>
+      <c r="D64" s="17" t="s">
+        <v>177</v>
+      </c>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -2117,10 +2244,12 @@
       <c r="C65" s="4">
         <v>24</v>
       </c>
-      <c r="D65" s="5"/>
+      <c r="D65" s="17" t="s">
+        <v>25</v>
+      </c>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -2130,10 +2259,12 @@
       <c r="C66" s="4">
         <v>25</v>
       </c>
-      <c r="D66" s="5"/>
+      <c r="D66" s="15" t="s">
+        <v>178</v>
+      </c>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -2143,10 +2274,12 @@
       <c r="C67" s="4">
         <v>26</v>
       </c>
-      <c r="D67" s="5"/>
+      <c r="D67" s="16" t="s">
+        <v>179</v>
+      </c>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -2156,10 +2289,12 @@
       <c r="C68" s="4">
         <v>27</v>
       </c>
-      <c r="D68" s="5"/>
+      <c r="D68" s="16" t="s">
+        <v>180</v>
+      </c>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -2169,10 +2304,12 @@
       <c r="C69" s="4">
         <v>28</v>
       </c>
-      <c r="D69" s="5"/>
+      <c r="D69" s="16" t="s">
+        <v>180</v>
+      </c>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2182,10 +2319,12 @@
       <c r="C70" s="4">
         <v>29</v>
       </c>
-      <c r="D70" s="5"/>
+      <c r="D70" s="17" t="s">
+        <v>181</v>
+      </c>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2195,10 +2334,12 @@
       <c r="C71" s="4">
         <v>30</v>
       </c>
-      <c r="D71" s="5"/>
+      <c r="D71" s="16" t="s">
+        <v>182</v>
+      </c>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2208,10 +2349,12 @@
       <c r="C72" s="4">
         <v>31</v>
       </c>
-      <c r="D72" s="5"/>
+      <c r="D72" s="16" t="s">
+        <v>183</v>
+      </c>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2221,10 +2364,12 @@
       <c r="C73" s="4">
         <v>32</v>
       </c>
-      <c r="D73" s="5"/>
+      <c r="D73" s="16" t="s">
+        <v>184</v>
+      </c>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2234,10 +2379,12 @@
       <c r="C74" s="4">
         <v>33</v>
       </c>
-      <c r="D74" s="5"/>
+      <c r="D74" s="17" t="s">
+        <v>185</v>
+      </c>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2247,10 +2394,12 @@
       <c r="C75" s="4">
         <v>34</v>
       </c>
-      <c r="D75" s="5"/>
+      <c r="D75" s="17" t="s">
+        <v>42</v>
+      </c>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2260,10 +2409,12 @@
       <c r="C76" s="4">
         <v>35</v>
       </c>
-      <c r="D76" s="5"/>
+      <c r="D76" s="17" t="s">
+        <v>186</v>
+      </c>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2273,10 +2424,12 @@
       <c r="C77" s="4">
         <v>36</v>
       </c>
-      <c r="D77" s="5"/>
+      <c r="D77" s="17" t="s">
+        <v>187</v>
+      </c>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2286,10 +2439,12 @@
       <c r="C78" s="4">
         <v>37</v>
       </c>
-      <c r="D78" s="5"/>
+      <c r="D78" s="17" t="s">
+        <v>15</v>
+      </c>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2299,10 +2454,12 @@
       <c r="C79" s="4">
         <v>38</v>
       </c>
-      <c r="D79" s="5"/>
+      <c r="D79" s="17" t="s">
+        <v>188</v>
+      </c>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2312,10 +2469,12 @@
       <c r="C80" s="4">
         <v>39</v>
       </c>
-      <c r="D80" s="5"/>
+      <c r="D80" s="17" t="s">
+        <v>188</v>
+      </c>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2325,10 +2484,12 @@
       <c r="C81" s="4">
         <v>40</v>
       </c>
-      <c r="D81" s="5"/>
+      <c r="D81" s="17" t="s">
+        <v>15</v>
+      </c>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2338,14 +2499,14 @@
       <c r="C82" s="4">
         <v>1</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="D82" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E82" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="E82" s="13" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2355,12 +2516,12 @@
       <c r="C83" s="4">
         <v>2</v>
       </c>
-      <c r="D83" s="5" t="s">
-        <v>169</v>
+      <c r="D83" s="16" t="s">
+        <v>190</v>
       </c>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2370,12 +2531,12 @@
       <c r="C84" s="4">
         <v>3</v>
       </c>
-      <c r="D84" s="5" t="s">
-        <v>170</v>
+      <c r="D84" s="16" t="s">
+        <v>190</v>
       </c>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2385,97 +2546,97 @@
       <c r="C85" s="4">
         <v>4</v>
       </c>
-      <c r="D85" s="5" t="s">
+      <c r="D85" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E85" s="11"/>
+    </row>
+    <row r="86" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B86" s="4">
+        <v>8</v>
+      </c>
+      <c r="C86" s="4">
+        <v>5</v>
+      </c>
+      <c r="D86" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B87" s="4">
+        <v>8</v>
+      </c>
+      <c r="C87" s="4">
+        <v>6</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B88" s="4">
+        <v>8</v>
+      </c>
+      <c r="C88" s="4">
+        <v>7</v>
+      </c>
+      <c r="D88" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E88" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B89" s="4">
+        <v>8</v>
+      </c>
+      <c r="C89" s="4">
+        <v>8</v>
+      </c>
+      <c r="D89" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E89" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="E85" s="11"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B86" s="4">
-        <v>8</v>
-      </c>
-      <c r="C86" s="4">
-        <v>5</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E86" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B87" s="4">
-        <v>8</v>
-      </c>
-      <c r="C87" s="4">
-        <v>6</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E87" s="13" t="s">
+    </row>
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B90" s="4">
+        <v>8</v>
+      </c>
+      <c r="C90" s="4">
+        <v>9</v>
+      </c>
+      <c r="D90" s="5" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B88" s="4">
-        <v>8</v>
-      </c>
-      <c r="C88" s="4">
-        <v>7</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E88" s="11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B89" s="4">
-        <v>8</v>
-      </c>
-      <c r="C89" s="4">
-        <v>8</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E89" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B90" s="4">
-        <v>8</v>
-      </c>
-      <c r="C90" s="4">
-        <v>9</v>
-      </c>
-      <c r="D90" s="5" t="s">
+      <c r="E90" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E90" s="11" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2485,10 +2646,14 @@
       <c r="C91" s="4">
         <v>10</v>
       </c>
-      <c r="D91" s="5"/>
-      <c r="E91" s="11"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D91" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E91" s="11" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2501,7 +2666,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2514,7 +2679,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2527,7 +2692,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2540,7 +2705,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2553,7 +2718,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2566,7 +2731,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2579,7 +2744,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2592,7 +2757,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2605,7 +2770,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2618,7 +2783,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2631,7 +2796,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2644,7 +2809,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2657,7 +2822,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2670,7 +2835,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2683,7 +2848,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2696,7 +2861,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2709,7 +2874,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2722,7 +2887,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2735,7 +2900,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2748,7 +2913,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2761,7 +2926,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2774,7 +2939,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2787,7 +2952,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2800,7 +2965,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2813,7 +2978,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2826,7 +2991,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -2839,7 +3004,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -2852,7 +3017,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -2865,7 +3030,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>
@@ -2878,7 +3043,7 @@
       <c r="D121" s="5"/>
       <c r="E121" s="11"/>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>5</v>
       </c>
@@ -2891,7 +3056,7 @@
       <c r="D122" s="5"/>
       <c r="E122" s="11"/>
     </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>5</v>
       </c>
@@ -2904,7 +3069,7 @@
       <c r="D123" s="5"/>
       <c r="E123" s="11"/>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>5</v>
       </c>
@@ -2917,7 +3082,7 @@
       <c r="D124" s="5"/>
       <c r="E124" s="11"/>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>5</v>
       </c>
@@ -2930,7 +3095,7 @@
       <c r="D125" s="5"/>
       <c r="E125" s="11"/>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>5</v>
       </c>
@@ -2943,7 +3108,7 @@
       <c r="D126" s="5"/>
       <c r="E126" s="11"/>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>5</v>
       </c>
@@ -2956,7 +3121,7 @@
       <c r="D127" s="5"/>
       <c r="E127" s="11"/>
     </row>
-    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>5</v>
       </c>
@@ -2969,7 +3134,7 @@
       <c r="D128" s="5"/>
       <c r="E128" s="11"/>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>5</v>
       </c>
@@ -2982,7 +3147,7 @@
       <c r="D129" s="5"/>
       <c r="E129" s="11"/>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>5</v>
       </c>
@@ -2995,7 +3160,7 @@
       <c r="D130" s="5"/>
       <c r="E130" s="11"/>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>5</v>
       </c>
@@ -3005,10 +3170,14 @@
       <c r="C131" s="4">
         <v>10</v>
       </c>
-      <c r="D131" s="5"/>
-      <c r="E131" s="11"/>
-    </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D131" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E131" s="11" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>5</v>
       </c>
@@ -3021,7 +3190,7 @@
       <c r="D132" s="5"/>
       <c r="E132" s="11"/>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>5</v>
       </c>
@@ -3034,7 +3203,7 @@
       <c r="D133" s="5"/>
       <c r="E133" s="11"/>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>5</v>
       </c>
@@ -3047,7 +3216,7 @@
       <c r="D134" s="5"/>
       <c r="E134" s="11"/>
     </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>5</v>
       </c>
@@ -3060,7 +3229,7 @@
       <c r="D135" s="5"/>
       <c r="E135" s="11"/>
     </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>5</v>
       </c>
@@ -3073,7 +3242,7 @@
       <c r="D136" s="5"/>
       <c r="E136" s="11"/>
     </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>5</v>
       </c>
@@ -3086,7 +3255,7 @@
       <c r="D137" s="5"/>
       <c r="E137" s="11"/>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>5</v>
       </c>
@@ -3099,7 +3268,7 @@
       <c r="D138" s="5"/>
       <c r="E138" s="11"/>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>5</v>
       </c>
@@ -3112,7 +3281,7 @@
       <c r="D139" s="5"/>
       <c r="E139" s="11"/>
     </row>
-    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>5</v>
       </c>
@@ -3125,7 +3294,7 @@
       <c r="D140" s="5"/>
       <c r="E140" s="11"/>
     </row>
-    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>5</v>
       </c>
@@ -3138,7 +3307,7 @@
       <c r="D141" s="5"/>
       <c r="E141" s="11"/>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>5</v>
       </c>
@@ -3151,7 +3320,7 @@
       <c r="D142" s="5"/>
       <c r="E142" s="11"/>
     </row>
-    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>5</v>
       </c>
@@ -3164,7 +3333,7 @@
       <c r="D143" s="5"/>
       <c r="E143" s="11"/>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>5</v>
       </c>
@@ -3177,7 +3346,7 @@
       <c r="D144" s="5"/>
       <c r="E144" s="11"/>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>5</v>
       </c>
@@ -3190,7 +3359,7 @@
       <c r="D145" s="5"/>
       <c r="E145" s="11"/>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>5</v>
       </c>
@@ -3203,7 +3372,7 @@
       <c r="D146" s="5"/>
       <c r="E146" s="11"/>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>5</v>
       </c>
@@ -3216,7 +3385,7 @@
       <c r="D147" s="5"/>
       <c r="E147" s="11"/>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>5</v>
       </c>
@@ -3229,7 +3398,7 @@
       <c r="D148" s="5"/>
       <c r="E148" s="11"/>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>5</v>
       </c>
@@ -3242,7 +3411,7 @@
       <c r="D149" s="5"/>
       <c r="E149" s="11"/>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>5</v>
       </c>
@@ -3255,7 +3424,7 @@
       <c r="D150" s="5"/>
       <c r="E150" s="11"/>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>5</v>
       </c>
@@ -3268,7 +3437,7 @@
       <c r="D151" s="5"/>
       <c r="E151" s="11"/>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>5</v>
       </c>
@@ -3281,7 +3450,7 @@
       <c r="D152" s="5"/>
       <c r="E152" s="11"/>
     </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>5</v>
       </c>
@@ -3294,7 +3463,7 @@
       <c r="D153" s="5"/>
       <c r="E153" s="11"/>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>5</v>
       </c>
@@ -3307,7 +3476,7 @@
       <c r="D154" s="5"/>
       <c r="E154" s="11"/>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>5</v>
       </c>
@@ -3320,7 +3489,7 @@
       <c r="D155" s="5"/>
       <c r="E155" s="11"/>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>5</v>
       </c>
@@ -3333,7 +3502,7 @@
       <c r="D156" s="5"/>
       <c r="E156" s="11"/>
     </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>5</v>
       </c>
@@ -3346,7 +3515,7 @@
       <c r="D157" s="5"/>
       <c r="E157" s="11"/>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>5</v>
       </c>
@@ -3359,7 +3528,7 @@
       <c r="D158" s="5"/>
       <c r="E158" s="11"/>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>5</v>
       </c>
@@ -3372,7 +3541,7 @@
       <c r="D159" s="5"/>
       <c r="E159" s="11"/>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>5</v>
       </c>
@@ -3385,7 +3554,7 @@
       <c r="D160" s="5"/>
       <c r="E160" s="11"/>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>5</v>
       </c>
@@ -11062,6 +11231,78 @@
       <c r="E736" t="s">
         <v>138</v>
       </c>
+    </row>
+    <row r="737" spans="3:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C737" s="4">
+        <v>41</v>
+      </c>
+      <c r="D737" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="E737" s="18"/>
+    </row>
+    <row r="738" spans="3:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C738" s="4">
+        <v>42</v>
+      </c>
+      <c r="D738" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="E738" s="18"/>
+    </row>
+    <row r="739" spans="3:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C739" s="4">
+        <v>43</v>
+      </c>
+      <c r="D739" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="E739" s="18"/>
+    </row>
+    <row r="740" spans="3:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C740" s="4">
+        <v>44</v>
+      </c>
+      <c r="D740" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E740" s="18"/>
+    </row>
+    <row r="741" spans="3:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C741" s="4">
+        <v>45</v>
+      </c>
+      <c r="D741" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="E741" s="18"/>
+    </row>
+    <row r="742" spans="3:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C742" s="4">
+        <v>46</v>
+      </c>
+      <c r="D742" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E742" s="18"/>
+    </row>
+    <row r="743" spans="3:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C743" s="4">
+        <v>47</v>
+      </c>
+      <c r="D743" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E743" s="18"/>
+    </row>
+    <row r="744" spans="3:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C744" s="4">
+        <v>48</v>
+      </c>
+      <c r="D744" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E744" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11081,13 +11322,13 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A736</xm:sqref>
+          <xm:sqref>A2:A744</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B736</xm:sqref>
+          <xm:sqref>B2:B744</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE167E8-BCB1-4338-BCC4-CAEBEFA3C8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1AE5764-E3DC-486E-B207-4A37B5C23836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -684,19 +684,19 @@
     <t>https://script.google.com/macros/s/AKfycbznanFehKu46uR9ojkTXUyOEzNR5dppsAFM5HLdc-7-g1ai9MoqDhJlW2xU4jbvzeLXNw/exec</t>
   </si>
   <si>
-    <t>https://script.google.com/macros/s/AKfycbzWu-Uo2ZMqu-xFx7PO2bQ8uvY82UlH5CYZzZGiTUXblUgKQdSjCj5xaJ7Q2meywc0r/exec</t>
-  </si>
-  <si>
     <t>https://script.google.com/macros/s/AKfycbzy8gZFRDPz_2ab2j6LZWFwj6Jp1WbsUIg2HNe9UriZFeKohBPwVIcBUdXC4tzp0PVB/exec</t>
   </si>
   <si>
     <t>Бесконечни периодични децимални броеви</t>
   </si>
   <si>
-    <t>https://script.google.com/macros/s/AKfycbxps3m-aLDJ60M-rwB1i2chsPVpltTpyxgpK7boq4rWBPCoIB6NddqZW8Iw2pA0C2NT/exec</t>
-  </si>
-  <si>
     <t>Операции со дропки</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbxnbzcerFn9RLkAVW8m3-fYSoAOioAqOqMtGVSd79Sef5aFE2COWlbldGO139SoQCzl/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbzpEq_6l7gYToO62oMrJUpmX6urEvc5YT1BNyfpzF3gRX217S9s0gjfRIO8y2X-_sK3/exec</t>
   </si>
 </sst>
 </file>
@@ -2126,7 +2126,7 @@
         <v>174</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2647,10 +2647,10 @@
         <v>10</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
@@ -3171,10 +3171,10 @@
         <v>10</v>
       </c>
       <c r="D131" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E131" s="11" t="s">
         <v>198</v>
-      </c>
-      <c r="E131" s="11" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1AE5764-E3DC-486E-B207-4A37B5C23836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636E077E-C8E1-4515-93CB-A0383FF03F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="200">
   <si>
     <t>Категорија</t>
   </si>
@@ -594,9 +594,6 @@
     <t>https://script.google.com/macros/s/AKfycbwivlQjcWhi72WQSK4uJKeXKFSecygPNRxguTqSO2WCt4s1ssSVmGlY9afFDSt9TJGk/exec</t>
   </si>
   <si>
-    <t>Рационални броеви</t>
-  </si>
-  <si>
     <t>https://script.google.com/macros/s/AKfycbzwaOeDsvA9sh7Wf2iKq8qOjzdw4jvZ3EMXZfRXmOOfJ23A4v0-Xm7UvTSzG2OVxwVJ/exec</t>
   </si>
   <si>
@@ -697,6 +694,12 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbzpEq_6l7gYToO62oMrJUpmX6urEvc5YT1BNyfpzF3gRX217S9s0gjfRIO8y2X-_sK3/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbz4nzIU2OMrnNP1BVR1GiTv2OWxZQqpfKFMsXkpN_8UXAF4SDMPoSK6iBGkwq1spMNlAA/exec</t>
+  </si>
+  <si>
+    <t>Операции со дропки-2</t>
   </si>
 </sst>
 </file>
@@ -882,7 +885,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -931,7 +934,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -964,7 +966,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="9"/>
+        <filter val="7"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1276,7 +1278,7 @@
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1895,7 +1897,7 @@
       </c>
       <c r="E41" s="11"/>
     </row>
-    <row r="42" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>5</v>
       </c>
@@ -1912,7 +1914,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
@@ -1927,7 +1929,7 @@
       </c>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
@@ -1942,7 +1944,7 @@
       </c>
       <c r="E44" s="11"/>
     </row>
-    <row r="45" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>5</v>
       </c>
@@ -1957,7 +1959,7 @@
       </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1970,7 +1972,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1983,7 +1985,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1996,7 +1998,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -2009,7 +2011,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -2022,7 +2024,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -2035,7 +2037,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -2048,7 +2050,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -2061,7 +2063,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -2072,13 +2074,13 @@
         <v>13</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -2089,13 +2091,13 @@
         <v>14</v>
       </c>
       <c r="D55" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="E55" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="E55" s="11" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -2106,13 +2108,13 @@
         <v>15</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -2123,13 +2125,13 @@
         <v>16</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -2140,11 +2142,11 @@
         <v>17</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -2155,11 +2157,11 @@
         <v>18</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -2174,7 +2176,7 @@
       </c>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -2189,7 +2191,7 @@
       </c>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -2204,7 +2206,7 @@
       </c>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -2215,11 +2217,11 @@
         <v>22</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -2230,11 +2232,11 @@
         <v>23</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -2249,7 +2251,7 @@
       </c>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -2260,11 +2262,11 @@
         <v>25</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -2275,11 +2277,11 @@
         <v>26</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -2290,11 +2292,11 @@
         <v>27</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -2305,11 +2307,11 @@
         <v>28</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2320,11 +2322,11 @@
         <v>29</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2335,11 +2337,11 @@
         <v>30</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2350,11 +2352,11 @@
         <v>31</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2365,11 +2367,11 @@
         <v>32</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2380,11 +2382,11 @@
         <v>33</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2399,7 +2401,7 @@
       </c>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2410,11 +2412,11 @@
         <v>35</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2425,11 +2427,11 @@
         <v>36</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2444,7 +2446,7 @@
       </c>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2455,11 +2457,11 @@
         <v>38</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2470,11 +2472,11 @@
         <v>39</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2500,7 +2502,7 @@
         <v>1</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E82" s="13" t="s">
         <v>159</v>
@@ -2517,7 +2519,7 @@
         <v>2</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E83" s="11"/>
     </row>
@@ -2532,7 +2534,7 @@
         <v>3</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E84" s="11"/>
     </row>
@@ -2562,7 +2564,7 @@
         <v>5</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E86" s="11" t="s">
         <v>162</v>
@@ -2579,7 +2581,7 @@
         <v>6</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E87" s="13" t="s">
         <v>163</v>
@@ -2599,7 +2601,7 @@
         <v>15</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2616,7 +2618,7 @@
         <v>25</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
@@ -2630,10 +2632,10 @@
         <v>9</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
@@ -2647,10 +2649,10 @@
         <v>10</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
@@ -3043,7 +3045,7 @@
       <c r="D121" s="5"/>
       <c r="E121" s="11"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>5</v>
       </c>
@@ -3056,7 +3058,7 @@
       <c r="D122" s="5"/>
       <c r="E122" s="11"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>5</v>
       </c>
@@ -3069,7 +3071,7 @@
       <c r="D123" s="5"/>
       <c r="E123" s="11"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>5</v>
       </c>
@@ -3082,7 +3084,7 @@
       <c r="D124" s="5"/>
       <c r="E124" s="11"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>5</v>
       </c>
@@ -3095,7 +3097,7 @@
       <c r="D125" s="5"/>
       <c r="E125" s="11"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>5</v>
       </c>
@@ -3108,7 +3110,7 @@
       <c r="D126" s="5"/>
       <c r="E126" s="11"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>5</v>
       </c>
@@ -3121,7 +3123,7 @@
       <c r="D127" s="5"/>
       <c r="E127" s="11"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>5</v>
       </c>
@@ -3134,7 +3136,7 @@
       <c r="D128" s="5"/>
       <c r="E128" s="11"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>5</v>
       </c>
@@ -3147,7 +3149,7 @@
       <c r="D129" s="5"/>
       <c r="E129" s="11"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>5</v>
       </c>
@@ -3160,7 +3162,7 @@
       <c r="D130" s="5"/>
       <c r="E130" s="11"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>5</v>
       </c>
@@ -3171,13 +3173,13 @@
         <v>10</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>5</v>
       </c>
@@ -3187,10 +3189,14 @@
       <c r="C132" s="4">
         <v>11</v>
       </c>
-      <c r="D132" s="5"/>
-      <c r="E132" s="11"/>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D132" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E132" s="11" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>5</v>
       </c>
@@ -3203,7 +3209,7 @@
       <c r="D133" s="5"/>
       <c r="E133" s="11"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>5</v>
       </c>
@@ -3216,7 +3222,7 @@
       <c r="D134" s="5"/>
       <c r="E134" s="11"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>5</v>
       </c>
@@ -3229,7 +3235,7 @@
       <c r="D135" s="5"/>
       <c r="E135" s="11"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>5</v>
       </c>
@@ -3242,7 +3248,7 @@
       <c r="D136" s="5"/>
       <c r="E136" s="11"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>5</v>
       </c>
@@ -3255,7 +3261,7 @@
       <c r="D137" s="5"/>
       <c r="E137" s="11"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>5</v>
       </c>
@@ -3268,7 +3274,7 @@
       <c r="D138" s="5"/>
       <c r="E138" s="11"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>5</v>
       </c>
@@ -3281,7 +3287,7 @@
       <c r="D139" s="5"/>
       <c r="E139" s="11"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>5</v>
       </c>
@@ -3294,7 +3300,7 @@
       <c r="D140" s="5"/>
       <c r="E140" s="11"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>5</v>
       </c>
@@ -3307,7 +3313,7 @@
       <c r="D141" s="5"/>
       <c r="E141" s="11"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>5</v>
       </c>
@@ -3320,7 +3326,7 @@
       <c r="D142" s="5"/>
       <c r="E142" s="11"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>5</v>
       </c>
@@ -3333,7 +3339,7 @@
       <c r="D143" s="5"/>
       <c r="E143" s="11"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>5</v>
       </c>
@@ -3346,7 +3352,7 @@
       <c r="D144" s="5"/>
       <c r="E144" s="11"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>5</v>
       </c>
@@ -3359,7 +3365,7 @@
       <c r="D145" s="5"/>
       <c r="E145" s="11"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>5</v>
       </c>
@@ -3372,7 +3378,7 @@
       <c r="D146" s="5"/>
       <c r="E146" s="11"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>5</v>
       </c>
@@ -3385,7 +3391,7 @@
       <c r="D147" s="5"/>
       <c r="E147" s="11"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>5</v>
       </c>
@@ -3398,7 +3404,7 @@
       <c r="D148" s="5"/>
       <c r="E148" s="11"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>5</v>
       </c>
@@ -3411,7 +3417,7 @@
       <c r="D149" s="5"/>
       <c r="E149" s="11"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>5</v>
       </c>
@@ -3424,7 +3430,7 @@
       <c r="D150" s="5"/>
       <c r="E150" s="11"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>5</v>
       </c>
@@ -3437,7 +3443,7 @@
       <c r="D151" s="5"/>
       <c r="E151" s="11"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>5</v>
       </c>
@@ -3450,7 +3456,7 @@
       <c r="D152" s="5"/>
       <c r="E152" s="11"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>5</v>
       </c>
@@ -3463,7 +3469,7 @@
       <c r="D153" s="5"/>
       <c r="E153" s="11"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>5</v>
       </c>
@@ -3476,7 +3482,7 @@
       <c r="D154" s="5"/>
       <c r="E154" s="11"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>5</v>
       </c>
@@ -3489,7 +3495,7 @@
       <c r="D155" s="5"/>
       <c r="E155" s="11"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>5</v>
       </c>
@@ -3502,7 +3508,7 @@
       <c r="D156" s="5"/>
       <c r="E156" s="11"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>5</v>
       </c>
@@ -3515,7 +3521,7 @@
       <c r="D157" s="5"/>
       <c r="E157" s="11"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>5</v>
       </c>
@@ -3528,7 +3534,7 @@
       <c r="D158" s="5"/>
       <c r="E158" s="11"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>5</v>
       </c>
@@ -3541,7 +3547,7 @@
       <c r="D159" s="5"/>
       <c r="E159" s="11"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>5</v>
       </c>
@@ -3554,7 +3560,7 @@
       <c r="D160" s="5"/>
       <c r="E160" s="11"/>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>5</v>
       </c>
@@ -11232,77 +11238,69 @@
         <v>138</v>
       </c>
     </row>
-    <row r="737" spans="3:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="3:4" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C737" s="4">
         <v>41</v>
       </c>
       <c r="D737" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="E737" s="18"/>
-    </row>
-    <row r="738" spans="3:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="738" spans="3:4" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C738" s="4">
         <v>42</v>
       </c>
       <c r="D738" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="E738" s="18"/>
-    </row>
-    <row r="739" spans="3:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="739" spans="3:4" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C739" s="4">
         <v>43</v>
       </c>
       <c r="D739" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="E739" s="18"/>
-    </row>
-    <row r="740" spans="3:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="740" spans="3:4" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C740" s="4">
         <v>44</v>
       </c>
       <c r="D740" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E740" s="18"/>
-    </row>
-    <row r="741" spans="3:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="741" spans="3:4" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C741" s="4">
         <v>45</v>
       </c>
       <c r="D741" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="E741" s="18"/>
-    </row>
-    <row r="742" spans="3:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="742" spans="3:4" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C742" s="4">
         <v>46</v>
       </c>
       <c r="D742" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E742" s="18"/>
-    </row>
-    <row r="743" spans="3:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="743" spans="3:4" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C743" s="4">
         <v>47</v>
       </c>
       <c r="D743" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E743" s="18"/>
-    </row>
-    <row r="744" spans="3:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="744" spans="3:4" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C744" s="4">
         <v>48</v>
       </c>
       <c r="D744" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="E744" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636E077E-C8E1-4515-93CB-A0383FF03F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A01A8CF3-2EF3-43A4-B34C-B4B0FE6CB00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="201">
   <si>
     <t>Категорија</t>
   </si>
@@ -700,6 +700,9 @@
   </si>
   <si>
     <t>Операции со дропки-2</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbylGClP88gz9fUqG8N-pv8QyNFzkQMoIFmcv6UE8A2G5NkNDkZxGSy2RLhEnCC8PgMF/exec</t>
   </si>
 </sst>
 </file>
@@ -966,7 +969,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="7"/>
+        <filter val="8"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1278,7 +1281,7 @@
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1897,7 +1900,7 @@
       </c>
       <c r="E41" s="11"/>
     </row>
-    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>5</v>
       </c>
@@ -1914,7 +1917,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
@@ -1929,7 +1932,7 @@
       </c>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
@@ -1944,7 +1947,7 @@
       </c>
       <c r="E44" s="11"/>
     </row>
-    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>5</v>
       </c>
@@ -1959,7 +1962,7 @@
       </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1972,7 +1975,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1985,7 +1988,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1998,7 +2001,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -2011,7 +2014,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -2024,7 +2027,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -2037,7 +2040,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -2050,7 +2053,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -2063,7 +2066,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -2080,7 +2083,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -2097,7 +2100,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -2114,7 +2117,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -2131,7 +2134,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -2146,7 +2149,7 @@
       </c>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -2161,7 +2164,7 @@
       </c>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -2176,7 +2179,7 @@
       </c>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -2191,7 +2194,7 @@
       </c>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -2206,7 +2209,7 @@
       </c>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -2221,7 +2224,7 @@
       </c>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -2236,7 +2239,7 @@
       </c>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -2251,7 +2254,7 @@
       </c>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -2266,7 +2269,7 @@
       </c>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -2281,7 +2284,7 @@
       </c>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -2296,7 +2299,7 @@
       </c>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -2311,7 +2314,7 @@
       </c>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2326,7 +2329,7 @@
       </c>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2341,7 +2344,7 @@
       </c>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2356,7 +2359,7 @@
       </c>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2371,7 +2374,7 @@
       </c>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2386,7 +2389,7 @@
       </c>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2401,7 +2404,7 @@
       </c>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2416,7 +2419,7 @@
       </c>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2431,7 +2434,7 @@
       </c>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2446,7 +2449,7 @@
       </c>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2461,7 +2464,7 @@
       </c>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2476,7 +2479,7 @@
       </c>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2491,7 +2494,7 @@
       </c>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2508,7 +2511,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2523,7 +2526,7 @@
       </c>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2538,7 +2541,7 @@
       </c>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2553,7 +2556,7 @@
       </c>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2570,7 +2573,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -2587,7 +2590,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -2604,7 +2607,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2621,7 +2624,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2638,7 +2641,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2655,7 +2658,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2668,7 +2671,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2681,7 +2684,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2691,10 +2694,14 @@
       <c r="C94" s="4">
         <v>13</v>
       </c>
-      <c r="D94" s="5"/>
-      <c r="E94" s="11"/>
-    </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D94" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E94" s="11" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2707,7 +2714,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2720,7 +2727,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2733,7 +2740,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2746,7 +2753,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2759,7 +2766,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2772,7 +2779,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2785,7 +2792,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2798,7 +2805,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2811,7 +2818,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2824,7 +2831,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2837,7 +2844,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2850,7 +2857,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2863,7 +2870,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2876,7 +2883,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2889,7 +2896,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2902,7 +2909,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2915,7 +2922,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2928,7 +2935,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2941,7 +2948,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2954,7 +2961,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2967,7 +2974,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2980,7 +2987,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2993,7 +3000,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -3006,7 +3013,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -3019,7 +3026,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -3032,7 +3039,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A01A8CF3-2EF3-43A4-B34C-B4B0FE6CB00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266B0F32-FEF1-4F25-97B9-F801FEB5AA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="203">
   <si>
     <t>Категорија</t>
   </si>
@@ -703,6 +703,12 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbylGClP88gz9fUqG8N-pv8QyNFzkQMoIFmcv6UE8A2G5NkNDkZxGSy2RLhEnCC8PgMF/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbyXxoK5aMjoPgiPcM8cJVHOyH2Ol3yPXvczMmCwa-_7-VRiIY9uQe_vFd8U1VHYVNEA/exec</t>
+  </si>
+  <si>
+    <t>Упростување изрази</t>
   </si>
 </sst>
 </file>
@@ -964,12 +970,12 @@
   <autoFilter ref="A1:E744" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Броеви"/>
+        <filter val="Алгебра"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="8"/>
+        <filter val="9"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2494,7 +2500,7 @@
       </c>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2511,7 +2517,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2526,7 +2532,7 @@
       </c>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2541,7 +2547,7 @@
       </c>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2556,7 +2562,7 @@
       </c>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2573,7 +2579,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" ht="31.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -2590,7 +2596,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -2607,7 +2613,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2624,7 +2630,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2641,7 +2647,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2658,7 +2664,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2671,7 +2677,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2684,7 +2690,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2701,7 +2707,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2714,7 +2720,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2727,7 +2733,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2740,7 +2746,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2753,7 +2759,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2766,7 +2772,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2779,7 +2785,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2792,7 +2798,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2805,7 +2811,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2818,7 +2824,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2831,7 +2837,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2844,7 +2850,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2857,7 +2863,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2870,7 +2876,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2883,7 +2889,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2896,7 +2902,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2909,7 +2915,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2922,7 +2928,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2935,7 +2941,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2948,7 +2954,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2961,7 +2967,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2974,7 +2980,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2987,7 +2993,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -3000,7 +3006,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -3013,7 +3019,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -3026,7 +3032,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -3039,7 +3045,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>
@@ -5226,7 +5232,7 @@
       <c r="D281" s="5"/>
       <c r="E281" s="11"/>
     </row>
-    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
         <v>43</v>
       </c>
@@ -5236,10 +5242,14 @@
       <c r="C282" s="4">
         <v>1</v>
       </c>
-      <c r="D282" s="5"/>
-      <c r="E282" s="11"/>
-    </row>
-    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D282" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E282" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
         <v>43</v>
       </c>
@@ -5252,7 +5262,7 @@
       <c r="D283" s="5"/>
       <c r="E283" s="11"/>
     </row>
-    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
         <v>43</v>
       </c>
@@ -5265,7 +5275,7 @@
       <c r="D284" s="5"/>
       <c r="E284" s="11"/>
     </row>
-    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
         <v>43</v>
       </c>
@@ -5278,7 +5288,7 @@
       <c r="D285" s="5"/>
       <c r="E285" s="11"/>
     </row>
-    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
         <v>43</v>
       </c>
@@ -5291,7 +5301,7 @@
       <c r="D286" s="5"/>
       <c r="E286" s="11"/>
     </row>
-    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
         <v>43</v>
       </c>
@@ -5304,7 +5314,7 @@
       <c r="D287" s="5"/>
       <c r="E287" s="11"/>
     </row>
-    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
         <v>43</v>
       </c>
@@ -5317,7 +5327,7 @@
       <c r="D288" s="5"/>
       <c r="E288" s="11"/>
     </row>
-    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
         <v>43</v>
       </c>
@@ -5330,7 +5340,7 @@
       <c r="D289" s="5"/>
       <c r="E289" s="11"/>
     </row>
-    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
         <v>43</v>
       </c>
@@ -5343,7 +5353,7 @@
       <c r="D290" s="5"/>
       <c r="E290" s="11"/>
     </row>
-    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
         <v>43</v>
       </c>
@@ -5356,7 +5366,7 @@
       <c r="D291" s="5"/>
       <c r="E291" s="11"/>
     </row>
-    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
         <v>43</v>
       </c>
@@ -5369,7 +5379,7 @@
       <c r="D292" s="5"/>
       <c r="E292" s="11"/>
     </row>
-    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
         <v>43</v>
       </c>
@@ -5382,7 +5392,7 @@
       <c r="D293" s="5"/>
       <c r="E293" s="11"/>
     </row>
-    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
         <v>43</v>
       </c>
@@ -5395,7 +5405,7 @@
       <c r="D294" s="5"/>
       <c r="E294" s="11"/>
     </row>
-    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
         <v>43</v>
       </c>
@@ -5408,7 +5418,7 @@
       <c r="D295" s="5"/>
       <c r="E295" s="11"/>
     </row>
-    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>43</v>
       </c>
@@ -5421,7 +5431,7 @@
       <c r="D296" s="5"/>
       <c r="E296" s="11"/>
     </row>
-    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
         <v>43</v>
       </c>
@@ -5434,7 +5444,7 @@
       <c r="D297" s="5"/>
       <c r="E297" s="11"/>
     </row>
-    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
         <v>43</v>
       </c>
@@ -5447,7 +5457,7 @@
       <c r="D298" s="5"/>
       <c r="E298" s="11"/>
     </row>
-    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
         <v>43</v>
       </c>
@@ -5460,7 +5470,7 @@
       <c r="D299" s="5"/>
       <c r="E299" s="11"/>
     </row>
-    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
         <v>43</v>
       </c>
@@ -5473,7 +5483,7 @@
       <c r="D300" s="5"/>
       <c r="E300" s="11"/>
     </row>
-    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
         <v>43</v>
       </c>
@@ -5486,7 +5496,7 @@
       <c r="D301" s="5"/>
       <c r="E301" s="11"/>
     </row>
-    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
         <v>43</v>
       </c>
@@ -5499,7 +5509,7 @@
       <c r="D302" s="5"/>
       <c r="E302" s="11"/>
     </row>
-    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
         <v>43</v>
       </c>
@@ -5512,7 +5522,7 @@
       <c r="D303" s="5"/>
       <c r="E303" s="11"/>
     </row>
-    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>43</v>
       </c>
@@ -5525,7 +5535,7 @@
       <c r="D304" s="5"/>
       <c r="E304" s="11"/>
     </row>
-    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
         <v>43</v>
       </c>
@@ -5538,7 +5548,7 @@
       <c r="D305" s="5"/>
       <c r="E305" s="11"/>
     </row>
-    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
         <v>43</v>
       </c>
@@ -5551,7 +5561,7 @@
       <c r="D306" s="5"/>
       <c r="E306" s="11"/>
     </row>
-    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
         <v>43</v>
       </c>
@@ -5564,7 +5574,7 @@
       <c r="D307" s="5"/>
       <c r="E307" s="11"/>
     </row>
-    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
         <v>43</v>
       </c>
@@ -5577,7 +5587,7 @@
       <c r="D308" s="5"/>
       <c r="E308" s="11"/>
     </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
         <v>43</v>
       </c>
@@ -5590,7 +5600,7 @@
       <c r="D309" s="5"/>
       <c r="E309" s="11"/>
     </row>
-    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
         <v>43</v>
       </c>
@@ -5603,7 +5613,7 @@
       <c r="D310" s="5"/>
       <c r="E310" s="11"/>
     </row>
-    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
         <v>43</v>
       </c>
@@ -5616,7 +5626,7 @@
       <c r="D311" s="5"/>
       <c r="E311" s="11"/>
     </row>
-    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
         <v>43</v>
       </c>
@@ -5629,7 +5639,7 @@
       <c r="D312" s="5"/>
       <c r="E312" s="11"/>
     </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
         <v>43</v>
       </c>
@@ -5642,7 +5652,7 @@
       <c r="D313" s="5"/>
       <c r="E313" s="11"/>
     </row>
-    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
         <v>43</v>
       </c>
@@ -5655,7 +5665,7 @@
       <c r="D314" s="5"/>
       <c r="E314" s="11"/>
     </row>
-    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
         <v>43</v>
       </c>
@@ -5668,7 +5678,7 @@
       <c r="D315" s="5"/>
       <c r="E315" s="11"/>
     </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
         <v>43</v>
       </c>
@@ -5685,7 +5695,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
         <v>43</v>
       </c>
@@ -5698,7 +5708,7 @@
       <c r="D317" s="5"/>
       <c r="E317" s="11"/>
     </row>
-    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
         <v>43</v>
       </c>
@@ -5715,7 +5725,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
         <v>43</v>
       </c>
@@ -5732,7 +5742,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
         <v>43</v>
       </c>
@@ -5747,7 +5757,7 @@
       </c>
       <c r="E320" s="11"/>
     </row>
-    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
         <v>43</v>
       </c>
